--- a/Result/checkall/2026-10-03.xlsx
+++ b/Result/checkall/2026-10-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR1"/>
+  <dimension ref="A1:GS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,610 +821,615 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>voc_cross</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>voc_cross_d</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>MA_5</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MA_10</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MA_80</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MA_240</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MA_50_斜率</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MA_80_斜率</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MA_240_斜率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_80</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>成交金額_補值</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>最小收盤價</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>下跌帶量_前15日次數</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>MA_break_前15日次數</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>抄底訊號_前15日次數</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>黃金交叉_前15日次數</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>量起點_前15日次數</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>價過5日_前15日次數</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前10日次數</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前5日次數</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前2日次數</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前1日次數</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>營業成本</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>營業毛利</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>稅後淨利</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>

--- a/Result/checkall/2026-10-03.xlsx
+++ b/Result/checkall/2026-10-03.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS1"/>
+  <dimension ref="A1:GT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,910 +526,915 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>TrendScore_15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>TrendType</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TrendScorertxt</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>BB_MID</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>BB_UPPER</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>BB_LOWER</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>BB_WIDTH</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>BB_MID_斜率</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>BB_UPPER_斜率</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>BB_WIDTH_斜率</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>BB_WIDTH_avg</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>BB_WIDTH_RATIO</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>BB_last_cross_date</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BB_golden_cross_area</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>BB_UPPER_pct_long</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>BB_UPPER_pct_short</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>BB_UPPER_cross</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>BB_UPPER_cross_date</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>up</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>up_last_cross_date</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>綜合Flag</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>綜合Flag_1d</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>綜合Flag_2d</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>綜合Flag_3d</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>up_up</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>up_up_3d</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>up_up_5d</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>up_up_10d</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>bbw_cross</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_d</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_3d</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_5d</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_10d</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_20d</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_30d</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MA_UP_40d</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MarketState</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MarketState_prev</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>score</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>外資_累計買賣超</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>投信_累計買進</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>投信_累計賣出</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>投信_累計買賣超</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>自營商_累計買賣超</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>三大法人_累計買賣超</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>交易日數</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>外資連續天數</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>投信連續天數</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>MA_break</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MACD_bottom_signal</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MACD_hist_diff</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>MACD_death_cross_d</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>MACD_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>MACD_death_cross_d2</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>MACD_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>voc_cross</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>voc_cross_d</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>MA_5</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>MA_10</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>MA_20</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>MA_50</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>MA_80</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>MA_240</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>MA_5_斜率</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>MA_10_斜率</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>MA_20_斜率</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>MA_50_斜率</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>MA_80_斜率</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>MA_240_斜率</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DC1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DD1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DG1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DH1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DI1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_5</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_10</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_30</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_50</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DO1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_80</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DP1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DQ1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DR1" s="1" t="inlineStr">
         <is>
           <t>成交金額_補值</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DS1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DV1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DW1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DX1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DY1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DZ1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EA1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EC1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EF1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EG1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EH1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EM1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EN1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EO1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>最小收盤價</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>下跌帶量_前15日次數</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>MA_break_前15日次數</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>抄底訊號_前15日次數</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
         <is>
           <t>黃金交叉_前15日次數</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FF1" s="1" t="inlineStr">
         <is>
           <t>量起點_前15日次數</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FG1" s="1" t="inlineStr">
         <is>
           <t>價過5日_前15日次數</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>量短5長30比</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前10日次數</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前5日次數</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前2日次數</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>checkpoint_前1日次數</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>季別</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>營業收入</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>營業成本</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>營業毛利</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>毛利率</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>營業利益</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>營益率</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>業外收支</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>稅前淨利</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FV1" s="1" t="inlineStr">
         <is>
           <t>稅後淨利</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FW1" s="1" t="inlineStr">
         <is>
           <t>EPS(元)</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FX1" s="1" t="inlineStr">
         <is>
           <t>EPS_前8季全為正</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>去年同季比較</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FZ1" s="1" t="inlineStr">
         <is>
           <t>EPS_MA_8</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="GA1" s="1" t="inlineStr">
         <is>
           <t>GM_MA_8</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GB1" s="1" t="inlineStr">
         <is>
           <t>EPS_維持</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GC1" s="1" t="inlineStr">
         <is>
           <t>毛利率_維持</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GD1" s="1" t="inlineStr">
         <is>
           <t>EPS_創新高</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GE1" s="1" t="inlineStr">
         <is>
           <t>毛利率_創新高</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GF1" s="1" t="inlineStr">
         <is>
           <t>財報健康</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GG1" s="1" t="inlineStr">
         <is>
           <t>財報強勢</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GH1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GI1" s="1" t="inlineStr">
         <is>
           <t>EPS_QoQ_%</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GJ1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GK1" s="1" t="inlineStr">
         <is>
           <t>GM_QoQ_%</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GL1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GM1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY_%</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GN1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GO1" s="1" t="inlineStr">
         <is>
           <t>GM_YoY_%</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GP1" s="1" t="inlineStr">
         <is>
           <t>EPS_成長</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GQ1" s="1" t="inlineStr">
         <is>
           <t>EPS_YoY成長</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GR1" s="1" t="inlineStr">
         <is>
           <t>毛利率成長</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GS1" s="1" t="inlineStr">
         <is>
           <t>毛利率YoY成長</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GT1" s="1" t="inlineStr">
         <is>
           <t>財報動能強</t>
         </is>
